--- a/output/pdf_financials_xlsx/SEGN.xlsx
+++ b/output/pdf_financials_xlsx/SEGN.xlsx
@@ -2622,7 +2622,7 @@
         <v>0.077587</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="93">
@@ -4890,7 +4890,11 @@
           <t>Share based payment reserve 18 44</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -4933,7 +4937,11 @@
           <t>Warrant reserve 17 158</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SEGN.xlsx
+++ b/output/pdf_financials_xlsx/SEGN.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.00184</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012032</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.014888</v>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.132954</v>
+        <v>-0.134794</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.086713</v>
+        <v>-0.098745</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.048799</v>
+        <v>-0.06368699999999999</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1162,13 +1162,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.132954</v>
+        <v>-0.134794</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.086713</v>
+        <v>-0.098745</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.237201</v>
+        <v>0.222313</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1280,19 +1280,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.20519</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.409547</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.35249</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.283418</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="35">
@@ -1324,19 +1324,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.20519</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.409547</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.35249</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.283418</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="37">
@@ -3360,10 +3360,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="125">
@@ -3384,10 +3384,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.052</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="126">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -6795,7 +6795,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -9437,7 +9441,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">

--- a/output/pdf_financials_xlsx/SEGN.xlsx
+++ b/output/pdf_financials_xlsx/SEGN.xlsx
@@ -2952,10 +2952,10 @@
         <v>0</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>1.011</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>0.582</v>
       </c>
     </row>
     <row r="108">
@@ -6071,7 +6071,11 @@
           <t>Share based payment expenses</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -6879,7 +6883,11 @@
           <t>Subscription receipts (Kalron Private Placement)</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -6959,7 +6967,11 @@
           <t>Proceeds from issuance of shares (Reem Private Placement)</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
